--- a/stories/arbres/ATOM-TMP.SEM.001-03.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Luce est dans sa chambre. Maman ouvre un livre des jours. Maman dit : il y a sept jours dans l'ordre. Lundi. Mardi. Mercredi. Jeudi. Vendredi. Samedi. Dimanche. Luce pose le doigt. Elle répète un jour : vendredi. Maman recommence. Luce dit : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.</t>
+          <t>Luce est dans sa chambre. Maman ouvre un livre des jours. Il y a sept jours dans l'ordre. Lundi. Mardi. Mercredi. Jeudi. Vendredi. Samedi. Dimanche. Luce pose le doigt. Elle répète un jour : vendredi. Maman recommence. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Luce est dans sa chambre. Maman ouvre un livre des jours.
+maman|Il y a sept jours dans l'ordre. Lundi. Mardi. Mercredi. Jeudi. Vendredi. Samedi. Dimanche.
+narrateur|Luce pose le doigt. Elle répète un jour : vendredi. Maman recommence.
+enfant-f|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Luce touche le livre. Que dit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Luce a dit les sept jours dans l'ordre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1825,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman ferme le livre. Luce s'allonge.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1992,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.001-03.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 enfant-f|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Luce touche le livre. Que dit-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Luce a dit les sept jours dans l'ordre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1838,7 @@
           <t>narrateur|Maman ferme le livre. Luce s'allonge.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2049,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2264,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SEM.001-03.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Luce dit les sept jours</t>
+          <t>Les crêpes de dimanche</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino veut une crêpe sucrée. Dimanche, la première se déchire. Il en réussit une autre. Lundi, il glisse un morceau dans le cartable. La sangle est tordue. Il la remet.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Luce est dans sa chambre. Maman ouvre un livre des jours. Il y a sept jours dans l'ordre. Lundi. Mardi. Mercredi. Jeudi. Vendredi. Samedi. Dimanche. Luce pose le doigt. Elle répète un jour : vendredi. Maman recommence. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.</t>
+          <t>La poêle chante un petit bruit de beurre. Une fumée douce monte vers la fenêtre. La table a une nappe à carreaux. Un bol de pâte tremble un peu. Tu as senti le beurre, Nino ? Il sent le gâteau. C'est dimanche. Dimanche, on fait des crêpes. En ce moment, Nino tient la spatule. La spatule est trop grande pour sa main. Je veux une crêpe sucrée. On la tourne ensemble ? Oui. La pâte s'étale, trop vite. Un trou s'ouvre au milieu. Elle se déchire. La première se déchire souvent. On recommence. Nino souffle sur la poêle. La deuxième crêpe reste ronde. Elle dore, tout doux. Celle-là, elle tient. Bravo. Tu as attendu le bon moment. Maman plie la crêpe en deux. Le sucre tombe comme une neige. Elle est à moi. Oui. Nino mord un coin. Le sucre pique un peu, puis fond. J'en garde une pour demain ? Demain, c'est lundi. Lundi, c'est le cartable. La semaine a sept jours. Quel jour vient après dimanche ? Lundi. Oui. Une crêpe refroidit dans une serviette. La poêle se tait.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Luce est dans sa chambre. Maman ouvre un livre des jours. Maman dit : il y a &lt;emphasis level="moderate"&gt;sept&lt;/emphasis&gt; jours dans l'ordre. Lundi. Mardi. Mercredi. Jeudi. Vendredi. Samedi. Dimanche. Luce pose le doigt. Elle répète un jour : vendredi. Maman recommence. Luce dit : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La poêle chante un petit bruit de beurre. Une fumée douce monte vers la fenêtre. La table a une nappe à carreaux. Un bol de pâte tremble un peu. Tu as senti le beurre, Nino ? Il sent le gâteau. C'est dimanche. Dimanche, on fait des crêpes. En ce moment, Nino tient la spatule. La spatule est trop grande pour sa main. Je veux une crêpe sucrée. On la tourne ensemble ? Oui. La pâte s'étale, trop vite. Un trou s'ouvre au milieu. Elle se déchire. La première se déchire souvent. On recommence. Nino souffle sur la poêle. La deuxième crêpe reste ronde. Elle dore, tout doux. Celle-là, elle tient. Bravo. Tu as attendu le bon moment. Maman plie la crêpe en deux. Le sucre tombe comme une neige. Elle est à moi. Oui. Nino mord un coin. Le sucre pique un peu, puis fond. J'en garde une pour demain ? Demain, c'est lundi. Lundi, c'est le cartable. La semaine a sept jours. Quel jour vient après dimanche ? Lundi. Oui. Une crêpe refroidit dans une serviette. La poêle se tait.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,47 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Luce est dans sa chambre. Maman ouvre un livre des jours.
-maman|Il y a sept jours dans l'ordre. Lundi. Mardi. Mercredi. Jeudi. Vendredi. Samedi. Dimanche.
-narrateur|Luce pose le doigt. Elle répète un jour : vendredi. Maman recommence.
-enfant-f|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La poêle chante un petit bruit de beurre.
+narrateur|Une fumée douce monte vers la fenêtre.
+narrateur|La table a une nappe à carreaux.
+narrateur|Un bol de pâte tremble un peu.
+maman|Tu as senti le beurre, Nino ?
+enfant-m|Il sent le gâteau.
+maman|C'est dimanche.
+maman|Dimanche, on fait des crêpes.
+narrateur|En ce moment, Nino tient la spatule.
+narrateur|La spatule est trop grande pour sa main.
+enfant-m|Je veux une crêpe sucrée.
+maman|On la tourne ensemble ?
+enfant-m|Oui.
+narrateur|La pâte s'étale, trop vite.
+narrateur|Un trou s'ouvre au milieu.
+enfant-m|Elle se déchire.
+maman|La première se déchire souvent.
+maman|On recommence.
+narrateur|Nino souffle sur la poêle.
+narrateur|La deuxième crêpe reste ronde.
+narrateur|Elle dore, tout doux.
+enfant-m|Celle-là, elle tient.
+maman|Bravo.
+maman|Tu as attendu le bon moment.
+narrateur|Maman plie la crêpe en deux.
+narrateur|Le sucre tombe comme une neige.
+enfant-m|Elle est à moi.
+maman|Oui.
+narrateur|Nino mord un coin.
+narrateur|Le sucre pique un peu, puis fond.
+enfant-m|J'en garde une pour demain ?
+maman|Demain, c'est lundi.
+maman|Lundi, c'est le cartable.
+maman|La semaine a sept jours.
+maman|Quel jour vient après dimanche ?
+enfant-m|Lundi.
+maman|Oui.
+narrateur|Une crêpe refroidit dans une serviette.
+narrateur|La poêle se tait.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1389,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Luce touche le livre. Que dit-elle ?</t>
+          <t>Après dimanche, quel jour vient ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Luce touche le livre. Que dit-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après dimanche, quel jour vient ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,7 +1409,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>lundi | vendredi | sept jours | un jour</t>
+          <t>lundi | le lundi | c'est lundi</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1378,7 +1424,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il y a sept jours. Dans quel ordre ?</t>
+          <t>Dimanche, les crêpes. Quel jour vient après ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1427,7 +1473,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1499,10 +1545,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Luce touche le livre. Que dit-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Après dimanche, quel jour vient ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,12 +1572,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Luce a dit les sept jours dans l'ordre.</t>
+          <t>Le lendemain, l'entrée sent encore le beurre. Le cartable bleu attend près des chaussures. C'est lundi, Nino. Le jour du cartable. Ma crêpe ? La serviette est sur la table. Nino glisse le morceau dans une boîte. Il pose la boîte dans le cartable. Elle vient avec moi. Oui. La sangle du cartable est tordue. Elle refuse de passer. Elle est de travers. Tu peux la remettre. Nino tourne la sangle tout doux. Elle se cale sur l'épaule. Merci, Nino. Tu as préparé ton lundi. La boîte fait un petit bruit de carton.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Luce a dit les &lt;emphasis level="moderate"&gt;sept&lt;/emphasis&gt; jours dans l'ordre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le lendemain, l'entrée sent encore le beurre. Le cartable bleu attend près des chaussures. C'est lundi, Nino. Le jour du cartable. Ma crêpe ? La serviette est sur la table. Nino glisse le morceau dans une boîte. Il pose la boîte dans le cartable. Elle vient avec moi. Oui. La sangle du cartable est tordue. Elle refuse de passer. Elle est de travers. Tu peux la remettre. Nino tourne la sangle tout doux. Elle se cale sur l'épaule. Merci, Nino. Tu as préparé ton lundi. La boîte fait un petit bruit de carton.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1595,7 +1640,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1671,10 +1716,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Luce a dit les sept jours dans l'ordre.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le lendemain, l'entrée sent encore le beurre.
+narrateur|Le cartable bleu attend près des chaussures.
+maman|C'est lundi, Nino.
+maman|Le jour du cartable.
+enfant-m|Ma crêpe ?
+narrateur|La serviette est sur la table.
+narrateur|Nino glisse le morceau dans une boîte.
+narrateur|Il pose la boîte dans le cartable.
+enfant-m|Elle vient avec moi.
+maman|Oui.
+narrateur|La sangle du cartable est tordue.
+narrateur|Elle refuse de passer.
+enfant-m|Elle est de travers.
+maman|Tu peux la remettre.
+narrateur|Nino tourne la sangle tout doux.
+narrateur|Elle se cale sur l'épaule.
+maman|Merci, Nino.
+maman|Tu as préparé ton lundi.
+narrateur|La boîte fait un petit bruit de carton.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,12 +1761,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman ferme le livre. Luce s'allonge.</t>
+          <t>Ils ouvrent la porte. L'air frais entre. Dimanche, les crêpes. Lundi, le cartable. Et ma crêpe dedans. Oui. Nino touche la boîte à travers le tissu. Elle est un peu chaude encore. Elle sent le sucre. Tu la mangeras à l'école. Les chaussures tapent le palier. Un oiseau crie dehors. On y va ? Oui, maman. La poêle, derrière, est déjà froide. La nappe a une miette de sucre. J'ai réussi la ronde. Oui. La première s'était déchirée.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman ferme le livre. Luce s'allonge.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils ouvrent la porte. L'air frais entre. Dimanche, les crêpes. Lundi, le cartable. Et ma crêpe dedans. Oui. Nino touche la boîte à travers le tissu. Elle est un peu chaude encore. Elle sent le sucre. Tu la mangeras à l'école. Les chaussures tapent le palier. Un oiseau crie dehors. On y va ? Oui, maman. La poêle, derrière, est déjà froide. La nappe a une miette de sucre. J'ai réussi la ronde. Oui. La première s'était déchirée.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,7 +1829,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1897,27 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman ferme le livre. Luce s'allonge.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils ouvrent la porte.
+narrateur|L'air frais entre.
+maman|Dimanche, les crêpes.
+maman|Lundi, le cartable.
+enfant-m|Et ma crêpe dedans.
+maman|Oui.
+narrateur|Nino touche la boîte à travers le tissu.
+narrateur|Elle est un peu chaude encore.
+enfant-m|Elle sent le sucre.
+maman|Tu la mangeras à l'école.
+narrateur|Les chaussures tapent le palier.
+narrateur|Un oiseau crie dehors.
+maman|On y va ?
+enfant-m|Oui, maman.
+narrateur|La poêle, derrière, est déjà froide.
+narrateur|La nappe a une miette de sucre.
+enfant-m|J'ai réussi la ronde.
+maman|Oui.
+maman|La première s'était déchirée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1863,12 +1942,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le cartable bleu tape la hanche de Nino. Ma crêpe voyage. Oui. Dimanche la poêle, lundi le cartable. Une miette de sucre brille encore sur la nappe.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cartable bleu tape la hanche de Nino. Ma crêpe voyage. Oui. Dimanche la poêle, lundi le cartable. Une miette de sucre brille encore sur la nappe.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1924,14 +2003,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2003,10 +2082,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le cartable bleu tape la hanche de Nino.
+enfant-m|Ma crêpe voyage.
+maman|Oui.
+maman|Dimanche la poêle, lundi le cartable.
+narrateur|Une miette de sucre brille encore sur la nappe.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2063,6 +2145,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.001-03.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre</t>
+          <t>cuisine le dimanche, puis entrée le lundi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Luce, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
